--- a/experiment/ELAN_bestx3/Test/results-B100/B100.xlsx
+++ b/experiment/ELAN_bestx3/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.81</v>
+        <v>25.02</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5994</v>
+        <v>0.6607</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.86</v>
+        <v>30.18</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7912</v>
+        <v>0.8632</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.44</v>
+        <v>27.82</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7498</v>
+        <v>0.8573</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.29</v>
+        <v>32.31</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8148</v>
+        <v>0.9023</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.27</v>
+        <v>27.5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7337</v>
+        <v>0.7901</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.21</v>
+        <v>35.38</v>
       </c>
       <c r="C7" t="n">
-        <v>0.84</v>
+        <v>0.9194</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.41</v>
+        <v>28.53</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7627</v>
+        <v>0.8465</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.52</v>
+        <v>24.42</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6412</v>
+        <v>0.7103</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.24</v>
+        <v>28.97</v>
       </c>
       <c r="C10" t="n">
-        <v>0.766</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28.5</v>
+        <v>30.9</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7766</v>
+        <v>0.8619</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23.33</v>
+        <v>26.43</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.8239</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.42</v>
+        <v>30.39</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7427</v>
+        <v>0.8483000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.3</v>
+        <v>31.84</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7977</v>
+        <v>0.8783</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.86</v>
+        <v>31.03</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7628</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24.96</v>
+        <v>26.47</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6894</v>
+        <v>0.7706</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.37</v>
+        <v>27.46</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7579</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.98</v>
+        <v>36.17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7996</v>
+        <v>0.9218</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29.89</v>
+        <v>34.47</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7987</v>
+        <v>0.9225</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24.85</v>
+        <v>27.34</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6948</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.88</v>
+        <v>27.44</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7614</v>
+        <v>0.8477</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.92</v>
+        <v>23.96</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6748</v>
+        <v>0.7947</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.71</v>
+        <v>25.63</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.7483</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24.88</v>
+        <v>25.75</v>
       </c>
       <c r="C24" t="n">
-        <v>0.595</v>
+        <v>0.6573</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24.96</v>
+        <v>28.21</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.8659</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26.75</v>
+        <v>29.72</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7998</v>
+        <v>0.8846000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26.88</v>
+        <v>28.8</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7781</v>
+        <v>0.8887</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.05</v>
+        <v>29.36</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7282</v>
+        <v>0.8085</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.21</v>
+        <v>31.37</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7655</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.76</v>
+        <v>34.42</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8213</v>
+        <v>0.9304</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.08</v>
+        <v>20.91</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5448</v>
+        <v>0.6109</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28.9</v>
+        <v>31.81</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8854</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.35</v>
+        <v>22.04</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5037</v>
+        <v>0.5715</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.32</v>
+        <v>26.91</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7169</v>
+        <v>0.7802</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.84</v>
+        <v>25.72</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7187</v>
+        <v>0.8202</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.93</v>
+        <v>36.82</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8183</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26.54</v>
+        <v>28.68</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7249</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.92</v>
+        <v>28.58</v>
       </c>
       <c r="C38" t="n">
-        <v>0.53</v>
+        <v>0.5812</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26.17</v>
+        <v>29.27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6825</v>
+        <v>0.7729</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>27.93</v>
+        <v>30.34</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7411</v>
+        <v>0.8378</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.63</v>
+        <v>39.38</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8468</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25.76</v>
+        <v>28.72</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7179</v>
+        <v>0.8087</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.17</v>
+        <v>27.17</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6851</v>
+        <v>0.7883</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25.72</v>
+        <v>28.32</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7087</v>
+        <v>0.8164</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26.75</v>
+        <v>30.03</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.9213</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.91</v>
+        <v>26.21</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6653</v>
+        <v>0.7765</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>30.39</v>
+        <v>35.88</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7793</v>
+        <v>0.9026999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.69</v>
+        <v>24.48</v>
       </c>
       <c r="C48" t="n">
-        <v>0.645</v>
+        <v>0.7316</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25.03</v>
+        <v>26.32</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6807</v>
+        <v>0.7403</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25.25</v>
+        <v>30.09</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8107</v>
+        <v>0.9296</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29.69</v>
+        <v>33.41</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7975</v>
+        <v>0.8746</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.2</v>
+        <v>26.03</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6465</v>
+        <v>0.7082000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.64</v>
+        <v>24.59</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6983</v>
+        <v>0.7895</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28.42</v>
+        <v>33.5</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28.61</v>
+        <v>33.69</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7564</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26.22</v>
+        <v>29.92</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7463</v>
+        <v>0.8541</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.11</v>
+        <v>27.38</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6916</v>
+        <v>0.7876</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.49</v>
+        <v>22.34</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4883</v>
+        <v>0.5435</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.03</v>
+        <v>28.63</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6943</v>
+        <v>0.7921</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29.09</v>
+        <v>32.98</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7402</v>
+        <v>0.8342000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28.84</v>
+        <v>32.13</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7187</v>
+        <v>0.8248</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30.15</v>
+        <v>32.83</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7429</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>27.76</v>
+        <v>30.45</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7442</v>
+        <v>0.8458</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>29.1</v>
+        <v>37.15</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.9679</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.57</v>
+        <v>25.82</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7198</v>
+        <v>0.7785</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.43</v>
+        <v>27.31</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.7102000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>27.63</v>
+        <v>29.99</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7716</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.06</v>
+        <v>42.75</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8394</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.34</v>
+        <v>22.51</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6424</v>
+        <v>0.6997</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.95</v>
+        <v>23.87</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6865</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27.71</v>
+        <v>31.02</v>
       </c>
       <c r="C71" t="n">
-        <v>0.7668</v>
+        <v>0.8689</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.57</v>
+        <v>32.51</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7205</v>
+        <v>0.8653999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.2</v>
+        <v>26.88</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.7073</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.1</v>
+        <v>28.31</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6505</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>25.2</v>
+        <v>27.36</v>
       </c>
       <c r="C75" t="n">
-        <v>0.702</v>
+        <v>0.7625</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23.33</v>
+        <v>25.72</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6619</v>
+        <v>0.7733</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>28.59</v>
+        <v>31.85</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7412</v>
+        <v>0.8373</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.5</v>
+        <v>24.64</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5477</v>
+        <v>0.5993000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>28.29</v>
+        <v>31.55</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7837</v>
+        <v>0.8693</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.85</v>
+        <v>34.99</v>
       </c>
       <c r="C80" t="n">
-        <v>0.8334</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.5</v>
+        <v>30.86</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7509</v>
+        <v>0.8649</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>32.91</v>
+        <v>37.64</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.9538</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27.6</v>
+        <v>29.38</v>
       </c>
       <c r="C83" t="n">
-        <v>0.6761</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.5</v>
+        <v>23.42</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5727</v>
+        <v>0.6462</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.46</v>
+        <v>22.22</v>
       </c>
       <c r="C85" t="n">
-        <v>0.5992</v>
+        <v>0.7038</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>24.29</v>
+        <v>26.95</v>
       </c>
       <c r="C86" t="n">
-        <v>0.713</v>
+        <v>0.8484</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.09</v>
+        <v>26.36</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6419</v>
+        <v>0.7112000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.09</v>
+        <v>28.54</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6939</v>
+        <v>0.7769</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>29.72</v>
+        <v>32.62</v>
       </c>
       <c r="C89" t="n">
-        <v>0.7853</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.85</v>
+        <v>28.13</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5997</v>
+        <v>0.6461</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.57</v>
+        <v>26.99</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.7738</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28.17</v>
+        <v>30.66</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7178</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>24.94</v>
+        <v>28.42</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29.22</v>
+        <v>33.56</v>
       </c>
       <c r="C94" t="n">
-        <v>0.844</v>
+        <v>0.9293</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>24.97</v>
+        <v>27.76</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7244</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.18</v>
+        <v>28.93</v>
       </c>
       <c r="C96" t="n">
-        <v>0.747</v>
+        <v>0.8849</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.64</v>
+        <v>22.44</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3886</v>
+        <v>0.4185</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>26.32</v>
+        <v>27.94</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5886</v>
+        <v>0.6454</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25.43</v>
+        <v>27.74</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7764</v>
+        <v>0.8454</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.77</v>
+        <v>28.45</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7062</v>
+        <v>0.8099</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>24.1</v>
+        <v>26.79</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7013</v>
+        <v>0.8114</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.27</v>
+        <v>29.13</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.8068</v>
       </c>
     </row>
   </sheetData>
